--- a/data/employees/EMP041/AST-EMP041-06.xlsx
+++ b/data/employees/EMP041/AST-EMP041-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Inventory Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Equipment Inventory Tracker - Alex Garcia (Manufacturing)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Alex Garcia | Role: Architect | Location: Portland | Date: 2025-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>96</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Line ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OEE %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Downtime (min)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units Produced</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Defect Rate %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>99</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>EMP041</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNC Mill A</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12</v>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8</v>
+        <v>93</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>EMP041</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Assembly Arm B</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>91</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
+        <v>89</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>EMP041</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conveyor Unit C</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>45</v>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
+        <v>61</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>EMP041</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laser Cutter D</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1</v>
+        <v>69</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>69</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>94</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>68</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>68</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>98</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>91</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>83</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>63</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>84</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>62</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>64</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>87</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>74</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>74</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp041 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>98</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP041</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP041 contributes to ast emp041 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>